--- a/output/xlsx/AC_2023_hold_analysis.xlsx
+++ b/output/xlsx/AC_2023_hold_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,17 +429,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Win_Pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Win</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Handle</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Win_Pct</t>
         </is>
       </c>
     </row>
@@ -455,103 +455,103 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Borgata</t>
+          <t>Bally's AC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$0.01</t>
+          <t>$0.05</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Caesars</t>
+          <t>Bally's AC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$0.01</t>
+          <t>$0.25</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Golden Nugget</t>
+          <t>Bally's AC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$0.01</t>
+          <t>$0.50</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hard Rock</t>
+          <t>Bally's AC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$0.01</t>
+          <t>$1.00</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Harrah's</t>
+          <t>Borgata</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -560,118 +560,118 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ocean Resort</t>
+          <t>Borgata</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$0.01</t>
+          <t>$0.05</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Resorts</t>
+          <t>Borgata</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$0.01</t>
+          <t>$0.25</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tropicana</t>
+          <t>Borgata</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$0.01</t>
+          <t>$0.50</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bally's AC</t>
+          <t>Borgata</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$0.05</t>
+          <t>$1.00</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>16.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Borgata</t>
+          <t>Caesars</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$0.05</t>
+          <t>$0.01</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -686,103 +686,103 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>11.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hard Rock</t>
+          <t>Caesars</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$0.05</t>
+          <t>$0.25</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Harrah's</t>
+          <t>Caesars</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$0.05</t>
+          <t>$0.50</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ocean Resort</t>
+          <t>Caesars</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>$0.05</t>
+          <t>$1.00</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Resorts</t>
+          <t>Golden Nugget</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>$0.05</t>
+          <t>$0.01</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tropicana</t>
+          <t>Golden Nugget</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bally's AC</t>
+          <t>Golden Nugget</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -812,76 +812,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Borgata</t>
+          <t>Golden Nugget</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.50</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Caesars</t>
+          <t>Golden Nugget</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$1.00</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Golden Nugget</t>
+          <t>Hard Rock</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.01</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -892,23 +892,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.05</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Harrah's</t>
+          <t>Hard Rock</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -917,24 +917,24 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ocean Resort</t>
+          <t>Hard Rock</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.50</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -944,97 +944,97 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Resorts</t>
+          <t>Hard Rock</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$1.00</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tropicana</t>
+          <t>Harrah's</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.01</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bally's AC</t>
+          <t>Harrah's</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.05</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Borgata</t>
+          <t>Harrah's</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.25</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Golden Nugget</t>
+          <t>Harrah's</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1043,55 +1043,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hard Rock</t>
+          <t>Harrah's</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$1.00</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Harrah's</t>
+          <t>Ocean Resort</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.01</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1102,44 +1102,44 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.05</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Resorts</t>
+          <t>Ocean Resort</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.25</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tropicana</t>
+          <t>Ocean Resort</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1148,19 +1148,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bally's AC</t>
+          <t>Ocean Resort</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1169,103 +1169,103 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Borgata</t>
+          <t>Resorts</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.01</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Caesars</t>
+          <t>Resorts</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.05</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Golden Nugget</t>
+          <t>Resorts</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.25</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Hard Rock</t>
+          <t>Resorts</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.50</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Harrah's</t>
+          <t>Resorts</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1274,55 +1274,55 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ocean Resort</t>
+          <t>Tropicana</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.01</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Resorts</t>
+          <t>Tropicana</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.05</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1333,65 +1333,65 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.25</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bally's AC</t>
+          <t>Tropicana</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>$0.50</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Borgata</t>
+          <t>Tropicana</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>$1.00</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Caesars</t>
+          <t>Bally's AC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1400,82 +1400,82 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Golden Nugget</t>
+          <t>Bally's AC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Hard Rock</t>
+          <t>Bally's AC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>Multi-Denom</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>18.7</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Harrah's</t>
+          <t>Bally's AC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ocean Resort</t>
+          <t>Borgata</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1484,97 +1484,97 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Resorts</t>
+          <t>Borgata</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tropicana</t>
+          <t>Borgata</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>Multi-Denom</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bally's AC</t>
+          <t>Borgata</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Borgata</t>
+          <t>Caesars</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$5.00</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1585,170 +1585,170 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>12.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Golden Nugget</t>
+          <t>Caesars</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>Multi-Denom</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Hard Rock</t>
+          <t>Caesars</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Harrah's</t>
+          <t>Golden Nugget</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$5.00</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ocean Resort</t>
+          <t>Golden Nugget</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Resorts</t>
+          <t>Golden Nugget</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>Multi-Denom</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tropicana</t>
+          <t>Golden Nugget</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bally's AC</t>
+          <t>Hard Rock</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>$100</t>
+          <t>$5.00</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Borgata</t>
+          <t>Hard Rock</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1757,76 +1757,76 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Caesars</t>
+          <t>Hard Rock</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>$100</t>
+          <t>Multi-Denom</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Golden Nugget</t>
+          <t>Hard Rock</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>$100</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Hard Rock</t>
+          <t>Harrah's</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>$100</t>
+          <t>$5.00</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1841,103 +1841,103 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>15.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ocean Resort</t>
+          <t>Harrah's</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>$100</t>
+          <t>Multi-Denom</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>15.7</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Resorts</t>
+          <t>Harrah's</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>$100</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tropicana</t>
+          <t>Ocean Resort</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>$100</t>
+          <t>$5.00</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Bally's AC</t>
+          <t>Ocean Resort</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Multi-Denom</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Borgata</t>
+          <t>Ocean Resort</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1946,82 +1946,82 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Caesars</t>
+          <t>Ocean Resort</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Multi-Denom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Golden Nugget</t>
+          <t>Resorts</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Multi-Denom</t>
+          <t>$5.00</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Hard Rock</t>
+          <t>Resorts</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Multi-Denom</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Harrah's</t>
+          <t>Resorts</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2030,55 +2030,55 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ocean Resort</t>
+          <t>Resorts</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Multi-Denom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Resorts</t>
+          <t>Tropicana</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Multi-Denom</t>
+          <t>$5.00</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2089,206 +2089,59 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Multi-Denom</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Bally's AC</t>
+          <t>Tropicana</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Total Slots</t>
+          <t>Multi-Denom</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Borgata</t>
+          <t>Tropicana</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Total Slots</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Caesars</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Total Slots</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" t="n">
-        <v>9.6</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Golden Nugget</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Total Slots</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" t="n">
-        <v>9.699999999999999</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Hard Rock</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Total Slots</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="n">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Harrah's</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Total Slots</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" t="n">
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Ocean Resort</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Total Slots</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Resorts</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Total Slots</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="n">
-        <v>9.6</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Tropicana</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Total Slots</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
